--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/36.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/36.xlsx
@@ -426,13 +426,13 @@
         <v>-11.29929206999117</v>
       </c>
       <c r="E2">
-        <v>-16.17761771966335</v>
+        <v>-17.0480538225737</v>
       </c>
       <c r="F2">
-        <v>-5.162353495165317</v>
+        <v>-5.080730313130468</v>
       </c>
       <c r="G2">
-        <v>-9.125993337681477</v>
+        <v>-10.73811976730375</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.03552076232362</v>
       </c>
       <c r="E3">
-        <v>-16.35450897135097</v>
+        <v>-17.29756821192233</v>
       </c>
       <c r="F3">
-        <v>-5.629291774612357</v>
+        <v>-5.080266427384901</v>
       </c>
       <c r="G3">
-        <v>-9.272733268709672</v>
+        <v>-9.533935311758169</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.61934380237439</v>
       </c>
       <c r="E4">
-        <v>-16.51746158004298</v>
+        <v>-18.02017228085228</v>
       </c>
       <c r="F4">
-        <v>-5.510534538644811</v>
+        <v>-5.248559205672453</v>
       </c>
       <c r="G4">
-        <v>-8.665989724454207</v>
+        <v>-9.649516388170744</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.07442961573524</v>
       </c>
       <c r="E5">
-        <v>-17.36930376867783</v>
+        <v>-18.91746223462811</v>
       </c>
       <c r="F5">
-        <v>-5.618904875748654</v>
+        <v>-5.221204028929805</v>
       </c>
       <c r="G5">
-        <v>-7.691818662431649</v>
+        <v>-9.297734508622248</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.412497860332694</v>
       </c>
       <c r="E6">
-        <v>-17.44772788154267</v>
+        <v>-19.02905741959913</v>
       </c>
       <c r="F6">
-        <v>-5.346241946545377</v>
+        <v>-4.975261747038632</v>
       </c>
       <c r="G6">
-        <v>-7.62322084831241</v>
+        <v>-8.899608302069495</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.662386484488051</v>
       </c>
       <c r="E7">
-        <v>-17.37444811515055</v>
+        <v>-19.9849322416122</v>
       </c>
       <c r="F7">
-        <v>-5.234937532100819</v>
+        <v>-4.829518786190087</v>
       </c>
       <c r="G7">
-        <v>-8.01187227353177</v>
+        <v>-8.743353863161435</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.839231342434638</v>
       </c>
       <c r="E8">
-        <v>-17.90316104096808</v>
+        <v>-20.33563991113623</v>
       </c>
       <c r="F8">
-        <v>-5.244834037462065</v>
+        <v>-4.958522926930263</v>
       </c>
       <c r="G8">
-        <v>-8.801556564287361</v>
+        <v>-8.396104120456201</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.955110695230376</v>
       </c>
       <c r="E9">
-        <v>-18.70831919105786</v>
+        <v>-20.01221629750842</v>
       </c>
       <c r="F9">
-        <v>-5.31775687666531</v>
+        <v>-4.964335580995707</v>
       </c>
       <c r="G9">
-        <v>-7.581021324323321</v>
+        <v>-8.165875541473126</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.027746315723669</v>
       </c>
       <c r="E10">
-        <v>-18.99904269387629</v>
+        <v>-21.30936144921353</v>
       </c>
       <c r="F10">
-        <v>-5.098843394760082</v>
+        <v>-4.94727204086544</v>
       </c>
       <c r="G10">
-        <v>-6.739940814070543</v>
+        <v>-7.474696533238548</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.075099285723885</v>
       </c>
       <c r="E11">
-        <v>-19.58014100701456</v>
+        <v>-21.87714152029524</v>
       </c>
       <c r="F11">
-        <v>-5.352782735557882</v>
+        <v>-5.122144541433429</v>
       </c>
       <c r="G11">
-        <v>-6.899750778887782</v>
+        <v>-7.479596140636669</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.111688563869281</v>
       </c>
       <c r="E12">
-        <v>-21.39255404520844</v>
+        <v>-21.72427835169232</v>
       </c>
       <c r="F12">
-        <v>-4.556122751835333</v>
+        <v>-5.143087326111007</v>
       </c>
       <c r="G12">
-        <v>-5.932210739580385</v>
+        <v>-7.218089527398559</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.152845765985367</v>
       </c>
       <c r="E13">
-        <v>-21.62402699411051</v>
+        <v>-22.77212195232716</v>
       </c>
       <c r="F13">
-        <v>-4.899267321505806</v>
+        <v>-4.980044740422397</v>
       </c>
       <c r="G13">
-        <v>-6.05187702918842</v>
+        <v>-6.779710397633808</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.234116476424007</v>
       </c>
       <c r="E14">
-        <v>-20.75368598915432</v>
+        <v>-22.87865430335761</v>
       </c>
       <c r="F14">
-        <v>-4.929399185782637</v>
+        <v>-4.777877533932164</v>
       </c>
       <c r="G14">
-        <v>-5.743297768927413</v>
+        <v>-6.207747444813926</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.384274120636617</v>
       </c>
       <c r="E15">
-        <v>-22.60896556230481</v>
+        <v>-23.7283907515789</v>
       </c>
       <c r="F15">
-        <v>-5.188070989552631</v>
+        <v>-4.682737052618432</v>
       </c>
       <c r="G15">
-        <v>-4.625094802127784</v>
+        <v>-6.649039854653235</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6281791334229557</v>
       </c>
       <c r="E16">
-        <v>-22.70288158474988</v>
+        <v>-24.97143422431437</v>
       </c>
       <c r="F16">
-        <v>-4.736522948082204</v>
+        <v>-4.699857750099492</v>
       </c>
       <c r="G16">
-        <v>-4.793492322073893</v>
+        <v>-5.480778128754287</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.009597937056294314</v>
       </c>
       <c r="E17">
-        <v>-23.8345427107927</v>
+        <v>-24.80576905969177</v>
       </c>
       <c r="F17">
-        <v>-4.794227021361217</v>
+        <v>-4.292849367142789</v>
       </c>
       <c r="G17">
-        <v>-3.57083171187364</v>
+        <v>-4.817066716859042</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.5112221603155328</v>
       </c>
       <c r="E18">
-        <v>-24.37318658010905</v>
+        <v>-26.07185793665228</v>
       </c>
       <c r="F18">
-        <v>-4.234940687115284</v>
+        <v>-4.442052418632827</v>
       </c>
       <c r="G18">
-        <v>-3.991929793923395</v>
+        <v>-5.205542683164819</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.8777467185645418</v>
       </c>
       <c r="E19">
-        <v>-24.36980381002532</v>
+        <v>-26.35058551182438</v>
       </c>
       <c r="F19">
-        <v>-3.651250649182876</v>
+        <v>-4.344040815900993</v>
       </c>
       <c r="G19">
-        <v>-3.775903455303793</v>
+        <v>-4.706759339490526</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.124831655878839</v>
       </c>
       <c r="E20">
-        <v>-25.97316437412911</v>
+        <v>-26.7851197637044</v>
       </c>
       <c r="F20">
-        <v>-3.562364341760281</v>
+        <v>-3.960352632067901</v>
       </c>
       <c r="G20">
-        <v>-2.780813056018581</v>
+        <v>-4.021622076865119</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.2699628055722</v>
       </c>
       <c r="E21">
-        <v>-26.92367295444308</v>
+        <v>-27.91640955487859</v>
       </c>
       <c r="F21">
-        <v>-3.616667966850803</v>
+        <v>-3.826176165264645</v>
       </c>
       <c r="G21">
-        <v>-3.274474985743622</v>
+        <v>-4.5101030028212</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.339062692243819</v>
       </c>
       <c r="E22">
-        <v>-27.09325072060831</v>
+        <v>-28.58167861439742</v>
       </c>
       <c r="F22">
-        <v>-3.384158490763426</v>
+        <v>-3.454536585305272</v>
       </c>
       <c r="G22">
-        <v>-2.783292654627495</v>
+        <v>-4.171838080709549</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.364061942272631</v>
       </c>
       <c r="E23">
-        <v>-26.08782080752931</v>
+        <v>-28.17230909257803</v>
       </c>
       <c r="F23">
-        <v>-3.759468566684604</v>
+        <v>-3.283253400693613</v>
       </c>
       <c r="G23">
-        <v>-3.690223226201915</v>
+        <v>-4.710890900323537</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.374520221614044</v>
       </c>
       <c r="E24">
-        <v>-28.776253557085</v>
+        <v>-28.6730541629242</v>
       </c>
       <c r="F24">
-        <v>-3.650298026669657</v>
+        <v>-3.253261530507854</v>
       </c>
       <c r="G24">
-        <v>-3.717862970909291</v>
+        <v>-4.665390762431794</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.392948484362416</v>
       </c>
       <c r="E25">
-        <v>-29.12044022403798</v>
+        <v>-28.89535695196073</v>
       </c>
       <c r="F25">
-        <v>-3.298679258468545</v>
+        <v>-3.305748545884036</v>
       </c>
       <c r="G25">
-        <v>-2.347148143101752</v>
+        <v>-4.419645656506154</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.439658025271159</v>
       </c>
       <c r="E26">
-        <v>-29.3125018636513</v>
+        <v>-30.01499724375019</v>
       </c>
       <c r="F26">
-        <v>-3.23985606082835</v>
+        <v>-3.123728891364692</v>
       </c>
       <c r="G26">
-        <v>-3.58250469544511</v>
+        <v>-4.628815855313926</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.531626946868314</v>
       </c>
       <c r="E27">
-        <v>-27.18849358593764</v>
+        <v>-29.22710390081465</v>
       </c>
       <c r="F27">
-        <v>-3.665967424461012</v>
+        <v>-3.194845889629836</v>
       </c>
       <c r="G27">
-        <v>-3.942996620307428</v>
+        <v>-5.169278967327643</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.678589189430648</v>
       </c>
       <c r="E28">
-        <v>-29.54846253029497</v>
+        <v>-29.67063623054791</v>
       </c>
       <c r="F28">
-        <v>-2.869657840149848</v>
+        <v>-3.29347296934195</v>
       </c>
       <c r="G28">
-        <v>-4.578796822761077</v>
+        <v>-4.531174625178661</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.880758280870264</v>
       </c>
       <c r="E29">
-        <v>-28.14742512790588</v>
+        <v>-29.37974517419119</v>
       </c>
       <c r="F29">
-        <v>-2.981559507491824</v>
+        <v>-3.096290877881764</v>
       </c>
       <c r="G29">
-        <v>-2.822330607626581</v>
+        <v>-5.077182900970658</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.138736711286165</v>
       </c>
       <c r="E30">
-        <v>-28.00742282548475</v>
+        <v>-29.05846805724301</v>
       </c>
       <c r="F30">
-        <v>-2.89238658494786</v>
+        <v>-2.871442143535478</v>
       </c>
       <c r="G30">
-        <v>-4.39041022884885</v>
+        <v>-5.4141236048666</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.447321012204877</v>
       </c>
       <c r="E31">
-        <v>-28.01262604211956</v>
+        <v>-28.47192198987352</v>
       </c>
       <c r="F31">
-        <v>-2.513468968987491</v>
+        <v>-3.01224886303074</v>
       </c>
       <c r="G31">
-        <v>-5.208621490516342</v>
+        <v>-5.283893364442751</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.797565809737055</v>
       </c>
       <c r="E32">
-        <v>-28.10920480728115</v>
+        <v>-28.81418858384725</v>
       </c>
       <c r="F32">
-        <v>-2.473252559948978</v>
+        <v>-2.765590043336146</v>
       </c>
       <c r="G32">
-        <v>-4.872217094997761</v>
+        <v>-5.817847943926261</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.175185314435458</v>
       </c>
       <c r="E33">
-        <v>-27.60808387359234</v>
+        <v>-27.64028132378688</v>
       </c>
       <c r="F33">
-        <v>-3.212775073696028</v>
+        <v>-3.051445551796407</v>
       </c>
       <c r="G33">
-        <v>-3.392062252752996</v>
+        <v>-6.016424397008365</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.569100229355952</v>
       </c>
       <c r="E34">
-        <v>-27.37398893823983</v>
+        <v>-28.20235098914491</v>
       </c>
       <c r="F34">
-        <v>-3.240671174352704</v>
+        <v>-3.344116867246904</v>
       </c>
       <c r="G34">
-        <v>-3.834298168070998</v>
+        <v>-5.560605313342733</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.966022200900559</v>
       </c>
       <c r="E35">
-        <v>-26.56003196315315</v>
+        <v>-27.65177459081834</v>
       </c>
       <c r="F35">
-        <v>-3.225359631279358</v>
+        <v>-2.883845288657595</v>
       </c>
       <c r="G35">
-        <v>-5.07849387700421</v>
+        <v>-5.65096665383714</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.349316064911561</v>
       </c>
       <c r="E36">
-        <v>-28.18259325704945</v>
+        <v>-26.63275925571633</v>
       </c>
       <c r="F36">
-        <v>-3.232368447874445</v>
+        <v>-3.041726317059361</v>
       </c>
       <c r="G36">
-        <v>-4.35607325051553</v>
+        <v>-5.769712611785258</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.705460012993957</v>
       </c>
       <c r="E37">
-        <v>-25.28557446622646</v>
+        <v>-26.47104292042842</v>
       </c>
       <c r="F37">
-        <v>-2.905122733765903</v>
+        <v>-2.805544688275374</v>
       </c>
       <c r="G37">
-        <v>-4.447391338670786</v>
+        <v>-6.155136255103828</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.023087161188219</v>
       </c>
       <c r="E38">
-        <v>-25.17170145882958</v>
+        <v>-26.03399536547414</v>
       </c>
       <c r="F38">
-        <v>-2.878356526246645</v>
+        <v>-2.607075313871238</v>
       </c>
       <c r="G38">
-        <v>-3.816401358885698</v>
+        <v>-6.458206767587487</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.292925379720871</v>
       </c>
       <c r="E39">
-        <v>-23.49984772535979</v>
+        <v>-25.99629129088628</v>
       </c>
       <c r="F39">
-        <v>-3.605730203664238</v>
+        <v>-2.874377877610999</v>
       </c>
       <c r="G39">
-        <v>-5.425293385516102</v>
+        <v>-5.800116662017925</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.504201474961732</v>
       </c>
       <c r="E40">
-        <v>-23.9464820597883</v>
+        <v>-24.85441392748216</v>
       </c>
       <c r="F40">
-        <v>-3.033132833622719</v>
+        <v>-2.94947103940958</v>
       </c>
       <c r="G40">
-        <v>-5.268320558226019</v>
+        <v>-6.193018827709708</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.654375537610424</v>
       </c>
       <c r="E41">
-        <v>-24.01775571219502</v>
+        <v>-24.58928988822909</v>
       </c>
       <c r="F41">
-        <v>-3.096011718067021</v>
+        <v>-2.762953349893035</v>
       </c>
       <c r="G41">
-        <v>-4.897516284008871</v>
+        <v>-5.472399137994391</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.741480376870792</v>
       </c>
       <c r="E42">
-        <v>-23.16059709507516</v>
+        <v>-24.14914938552758</v>
       </c>
       <c r="F42">
-        <v>-2.7622624914791</v>
+        <v>-2.581265042334811</v>
       </c>
       <c r="G42">
-        <v>-4.341791557059113</v>
+        <v>-5.571232164523794</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.76663277029325</v>
       </c>
       <c r="E43">
-        <v>-23.01441795410756</v>
+        <v>-23.33343536252591</v>
       </c>
       <c r="F43">
-        <v>-2.975139660120128</v>
+        <v>-2.653260110046921</v>
       </c>
       <c r="G43">
-        <v>-4.543436885856122</v>
+        <v>-6.264470332083798</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.73175030851812</v>
       </c>
       <c r="E44">
-        <v>-22.69377029504645</v>
+        <v>-23.7399066609804</v>
       </c>
       <c r="F44">
-        <v>-3.195017361682215</v>
+        <v>-2.71435054926858</v>
       </c>
       <c r="G44">
-        <v>-5.052612031978187</v>
+        <v>-5.621893442911261</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.641969731949031</v>
       </c>
       <c r="E45">
-        <v>-22.18213877318584</v>
+        <v>-22.6329891169155</v>
       </c>
       <c r="F45">
-        <v>-3.197325193266414</v>
+        <v>-2.757799247912816</v>
       </c>
       <c r="G45">
-        <v>-5.040449087666905</v>
+        <v>-6.050549500427173</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.505558013380448</v>
       </c>
       <c r="E46">
-        <v>-19.74841457266558</v>
+        <v>-22.91979096124328</v>
       </c>
       <c r="F46">
-        <v>-2.921381929148052</v>
+        <v>-3.024580768556217</v>
       </c>
       <c r="G46">
-        <v>-4.790761122003993</v>
+        <v>-6.31946842512771</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.329718509971485</v>
       </c>
       <c r="E47">
-        <v>-20.18756786803343</v>
+        <v>-21.41274651080864</v>
       </c>
       <c r="F47">
-        <v>-2.79509234838685</v>
+        <v>-2.619968024128409</v>
       </c>
       <c r="G47">
-        <v>-4.638548859199383</v>
+        <v>-5.980392419358937</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.123212063239641</v>
       </c>
       <c r="E48">
-        <v>-19.88862065641707</v>
+        <v>-21.34052187886031</v>
       </c>
       <c r="F48">
-        <v>-2.643758735936811</v>
+        <v>-2.436074602543933</v>
       </c>
       <c r="G48">
-        <v>-5.073329425962946</v>
+        <v>-6.194594647386401</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.891110247232175</v>
       </c>
       <c r="E49">
-        <v>-19.32357578363599</v>
+        <v>-20.97285960265156</v>
       </c>
       <c r="F49">
-        <v>-2.805065891916556</v>
+        <v>-2.701549787793119</v>
       </c>
       <c r="G49">
-        <v>-4.108282227446621</v>
+        <v>-6.220056053128936</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.642679898111183</v>
       </c>
       <c r="E50">
-        <v>-18.2942400562705</v>
+        <v>-20.32608030250604</v>
       </c>
       <c r="F50">
-        <v>-2.676355821604374</v>
+        <v>-2.661111376290655</v>
       </c>
       <c r="G50">
-        <v>-4.818718679083139</v>
+        <v>-6.261093575633741</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.381255551018981</v>
       </c>
       <c r="E51">
-        <v>-19.61587066693508</v>
+        <v>-19.92560470363771</v>
       </c>
       <c r="F51">
-        <v>-3.048509817720886</v>
+        <v>-2.607816702696743</v>
       </c>
       <c r="G51">
-        <v>-5.731618164264865</v>
+        <v>-6.580796268906699</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.10874244254307</v>
       </c>
       <c r="E52">
-        <v>-18.30925647607993</v>
+        <v>-18.43880706049136</v>
       </c>
       <c r="F52">
-        <v>-2.435725031499952</v>
+        <v>-2.549348874672348</v>
       </c>
       <c r="G52">
-        <v>-4.99827273749659</v>
+        <v>-6.79310155434016</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.827003712791159</v>
       </c>
       <c r="E53">
-        <v>-15.66753946438737</v>
+        <v>-18.19367170550815</v>
       </c>
       <c r="F53">
-        <v>-2.743856996156298</v>
+        <v>-2.54293731097468</v>
       </c>
       <c r="G53">
-        <v>-4.673528083367322</v>
+        <v>-6.315912899218532</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.539801438402224</v>
       </c>
       <c r="E54">
-        <v>-17.26922449310832</v>
+        <v>-18.21375095925816</v>
       </c>
       <c r="F54">
-        <v>-2.755678627361649</v>
+        <v>-2.486474960432463</v>
       </c>
       <c r="G54">
-        <v>-6.148998503674019</v>
+        <v>-6.488647233821085</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.248259509358228</v>
       </c>
       <c r="E55">
-        <v>-17.09347441687063</v>
+        <v>-17.86077452425629</v>
       </c>
       <c r="F55">
-        <v>-2.953453001514837</v>
+        <v>-2.939841268352036</v>
       </c>
       <c r="G55">
-        <v>-5.346648065685176</v>
+        <v>-6.608300281246964</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.952500871377822</v>
       </c>
       <c r="E56">
-        <v>-15.21999943515733</v>
+        <v>-17.97675327206673</v>
       </c>
       <c r="F56">
-        <v>-2.416627021028409</v>
+        <v>-2.50661588546413</v>
       </c>
       <c r="G56">
-        <v>-6.109596390665613</v>
+        <v>-6.979958676213244</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.658781138793841</v>
       </c>
       <c r="E57">
-        <v>-16.24209413258456</v>
+        <v>-18.30427515467149</v>
       </c>
       <c r="F57">
-        <v>-2.859580750694791</v>
+        <v>-2.850410723545801</v>
       </c>
       <c r="G57">
-        <v>-4.999457912799649</v>
+        <v>-6.03838324557035</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.371031089675069</v>
       </c>
       <c r="E58">
-        <v>-15.53219696172013</v>
+        <v>-16.92937157578067</v>
       </c>
       <c r="F58">
-        <v>-2.992514666393848</v>
+        <v>-2.882554692244033</v>
       </c>
       <c r="G58">
-        <v>-5.220254747541341</v>
+        <v>-6.421026030635932</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.093447629505656</v>
       </c>
       <c r="E59">
-        <v>-15.73677077501664</v>
+        <v>-17.4185237526672</v>
       </c>
       <c r="F59">
-        <v>-3.515187989803446</v>
+        <v>-2.617673446422655</v>
       </c>
       <c r="G59">
-        <v>-5.454230864074871</v>
+        <v>-6.951233072568987</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.829995187322601</v>
       </c>
       <c r="E60">
-        <v>-14.55864750565513</v>
+        <v>-16.80285054048037</v>
       </c>
       <c r="F60">
-        <v>-3.23112424003544</v>
+        <v>-2.660274725213827</v>
       </c>
       <c r="G60">
-        <v>-5.902299960633069</v>
+        <v>-7.404741395448209</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.589472507279163</v>
       </c>
       <c r="E61">
-        <v>-14.21638091168139</v>
+        <v>-17.21888144756505</v>
       </c>
       <c r="F61">
-        <v>-3.239525542234632</v>
+        <v>-2.681827188299865</v>
       </c>
       <c r="G61">
-        <v>-5.8464709206588</v>
+        <v>-7.26991942836139</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.376603171832304</v>
       </c>
       <c r="E62">
-        <v>-14.23692206978019</v>
+        <v>-16.23966687051645</v>
       </c>
       <c r="F62">
-        <v>-2.791193223021873</v>
+        <v>-2.661050905470251</v>
       </c>
       <c r="G62">
-        <v>-5.952021044087383</v>
+        <v>-7.605002916209801</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.195602434333079</v>
       </c>
       <c r="E63">
-        <v>-15.61015011328817</v>
+        <v>-16.252391882478</v>
       </c>
       <c r="F63">
-        <v>-2.947672653778102</v>
+        <v>-2.844594756010746</v>
       </c>
       <c r="G63">
-        <v>-5.656703829256697</v>
+        <v>-7.316316724094275</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.052694580176557</v>
       </c>
       <c r="E64">
-        <v>-15.03777816956268</v>
+        <v>-16.10654332011296</v>
       </c>
       <c r="F64">
-        <v>-2.982188238350549</v>
+        <v>-3.107410881896945</v>
       </c>
       <c r="G64">
-        <v>-6.099721033321967</v>
+        <v>-7.041038241412798</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.9511760779745609</v>
       </c>
       <c r="E65">
-        <v>-13.61134508493858</v>
+        <v>-15.51360304744464</v>
       </c>
       <c r="F65">
-        <v>-3.172679606298324</v>
+        <v>-2.960714470167777</v>
       </c>
       <c r="G65">
-        <v>-5.836310856398777</v>
+        <v>-7.269336772346477</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.8926056282661887</v>
       </c>
       <c r="E66">
-        <v>-14.83598483930688</v>
+        <v>-16.06062459367518</v>
       </c>
       <c r="F66">
-        <v>-3.268831524210873</v>
+        <v>-2.671926541101605</v>
       </c>
       <c r="G66">
-        <v>-6.826468542830475</v>
+        <v>-7.396435236690177</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.8761081641658713</v>
       </c>
       <c r="E67">
-        <v>-12.55451699187252</v>
+        <v>-14.8532337968021</v>
       </c>
       <c r="F67">
-        <v>-2.820559675818518</v>
+        <v>-2.910468188616168</v>
       </c>
       <c r="G67">
-        <v>-6.607558719046168</v>
+        <v>-7.024108111524964</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.9022930409816425</v>
       </c>
       <c r="E68">
-        <v>-14.50489904765809</v>
+        <v>-15.79032450863135</v>
       </c>
       <c r="F68">
-        <v>-3.16254121765546</v>
+        <v>-3.061239339599706</v>
       </c>
       <c r="G68">
-        <v>-6.972731755301015</v>
+        <v>-7.172063012766072</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.9668664952231261</v>
       </c>
       <c r="E69">
-        <v>-13.62904688983456</v>
+        <v>-15.22988056544206</v>
       </c>
       <c r="F69">
-        <v>-3.011789947489589</v>
+        <v>-2.66237049474291</v>
       </c>
       <c r="G69">
-        <v>-5.522060631628999</v>
+        <v>-7.082926574121196</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.066971987396048</v>
       </c>
       <c r="E70">
-        <v>-13.425030078841</v>
+        <v>-16.17730978343083</v>
       </c>
       <c r="F70">
-        <v>-2.69437778281968</v>
+        <v>-3.131008584100494</v>
       </c>
       <c r="G70">
-        <v>-6.978594731451064</v>
+        <v>-7.217510181929187</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.199385787134717</v>
       </c>
       <c r="E71">
-        <v>-13.14304200238336</v>
+        <v>-15.48540423979887</v>
       </c>
       <c r="F71">
-        <v>-3.69227802990873</v>
+        <v>-2.903258078742201</v>
       </c>
       <c r="G71">
-        <v>-6.440396032586208</v>
+        <v>-7.11029816463989</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.359848225543491</v>
       </c>
       <c r="E72">
-        <v>-14.67427756096698</v>
+        <v>-15.82565566283919</v>
       </c>
       <c r="F72">
-        <v>-3.384229730360067</v>
+        <v>-3.388302812879632</v>
       </c>
       <c r="G72">
-        <v>-5.538967587698057</v>
+        <v>-6.996259802448615</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.544325267404595</v>
       </c>
       <c r="E73">
-        <v>-13.93325618824784</v>
+        <v>-15.86829124562141</v>
       </c>
       <c r="F73">
-        <v>-3.485399897998776</v>
+        <v>-3.17310455877596</v>
       </c>
       <c r="G73">
-        <v>-6.27418347269602</v>
+        <v>-7.019291267765325</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.750794472635697</v>
       </c>
       <c r="E74">
-        <v>-13.95469851267415</v>
+        <v>-16.39084544678851</v>
       </c>
       <c r="F74">
-        <v>-3.221552454696091</v>
+        <v>-3.488581657192929</v>
       </c>
       <c r="G74">
-        <v>-5.271008721203907</v>
+        <v>-6.911013254812382</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.978014833449729</v>
       </c>
       <c r="E75">
-        <v>-14.60326203157869</v>
+        <v>-16.56894127256217</v>
       </c>
       <c r="F75">
-        <v>-3.446553608644493</v>
+        <v>-3.396354544034843</v>
       </c>
       <c r="G75">
-        <v>-5.989933411603117</v>
+        <v>-6.517998530572264</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.2203966380068</v>
       </c>
       <c r="E76">
-        <v>-16.03834903003145</v>
+        <v>-17.30617684101091</v>
       </c>
       <c r="F76">
-        <v>-3.281895706520424</v>
+        <v>-3.231435706178893</v>
       </c>
       <c r="G76">
-        <v>-6.367739489635824</v>
+        <v>-6.630133329078458</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.478258346695557</v>
       </c>
       <c r="E77">
-        <v>-15.79410125595374</v>
+        <v>-16.72079006298738</v>
       </c>
       <c r="F77">
-        <v>-3.602491287119292</v>
+        <v>-3.310186110060833</v>
       </c>
       <c r="G77">
-        <v>-5.452731186945582</v>
+        <v>-7.062530303053746</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.749778852693787</v>
       </c>
       <c r="E78">
-        <v>-17.13227891064236</v>
+        <v>-17.20166871786189</v>
       </c>
       <c r="F78">
-        <v>-3.561166522495833</v>
+        <v>-3.225746478856465</v>
       </c>
       <c r="G78">
-        <v>-5.388380802753228</v>
+        <v>-6.45251593980548</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.032081445872868</v>
       </c>
       <c r="E79">
-        <v>-16.50943259562738</v>
+        <v>-17.924367884746</v>
       </c>
       <c r="F79">
-        <v>-3.519152556193245</v>
+        <v>-3.351801631642675</v>
       </c>
       <c r="G79">
-        <v>-4.944208218294752</v>
+        <v>-6.685353228673501</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.320799596101809</v>
       </c>
       <c r="E80">
-        <v>-17.60819435800447</v>
+        <v>-18.8141360431951</v>
       </c>
       <c r="F80">
-        <v>-3.431753996626077</v>
+        <v>-3.606665430461999</v>
       </c>
       <c r="G80">
-        <v>-5.12700330079115</v>
+        <v>-6.309963848884463</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.614788977930718</v>
       </c>
       <c r="E81">
-        <v>-17.76592110769163</v>
+        <v>-19.39616269350494</v>
       </c>
       <c r="F81">
-        <v>-3.338960280164477</v>
+        <v>-3.629341988113635</v>
       </c>
       <c r="G81">
-        <v>-4.425727128661795</v>
+        <v>-6.211170548901531</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.910869470255264</v>
       </c>
       <c r="E82">
-        <v>-18.57303555855272</v>
+        <v>-19.72748396580213</v>
       </c>
       <c r="F82">
-        <v>-3.501134736814953</v>
+        <v>-3.583611965642088</v>
       </c>
       <c r="G82">
-        <v>-4.718266795785033</v>
+        <v>-6.402208889790715</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.201104158060122</v>
       </c>
       <c r="E83">
-        <v>-20.03759839432141</v>
+        <v>-20.17829808173973</v>
       </c>
       <c r="F83">
-        <v>-3.676109126573487</v>
+        <v>-3.795259837057362</v>
       </c>
       <c r="G83">
-        <v>-5.718412398108712</v>
+        <v>-6.133435629093905</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.479790413245441</v>
       </c>
       <c r="E84">
-        <v>-22.31104631428819</v>
+        <v>-21.18900366703766</v>
       </c>
       <c r="F84">
-        <v>-4.277562675091526</v>
+        <v>-3.638739816298395</v>
       </c>
       <c r="G84">
-        <v>-4.93240943399279</v>
+        <v>-6.270839821701355</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.738729600086609</v>
       </c>
       <c r="E85">
-        <v>-19.85640056385249</v>
+        <v>-22.25156480819744</v>
       </c>
       <c r="F85">
-        <v>-3.891736474991809</v>
+        <v>-3.756378756272162</v>
       </c>
       <c r="G85">
-        <v>-4.715995761545093</v>
+        <v>-5.939017221209126</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.968516495307808</v>
       </c>
       <c r="E86">
-        <v>-21.72749809671177</v>
+        <v>-23.64806920810485</v>
       </c>
       <c r="F86">
-        <v>-3.59409329838971</v>
+        <v>-3.938082802811039</v>
       </c>
       <c r="G86">
-        <v>-4.184209589389805</v>
+        <v>-5.512764619754726</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.155847948215329</v>
       </c>
       <c r="E87">
-        <v>-23.72606311593895</v>
+        <v>-24.51671203530816</v>
       </c>
       <c r="F87">
-        <v>-4.280606925296815</v>
+        <v>-4.244147162429997</v>
       </c>
       <c r="G87">
-        <v>-3.608055485917205</v>
+        <v>-5.760989324289278</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.290141618755999</v>
       </c>
       <c r="E88">
-        <v>-25.0449539998289</v>
+        <v>-25.34477520692874</v>
       </c>
       <c r="F88">
-        <v>-4.256553621021725</v>
+        <v>-3.960514163711446</v>
       </c>
       <c r="G88">
-        <v>-4.221761107441758</v>
+        <v>-5.652393498964566</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.359951085296062</v>
       </c>
       <c r="E89">
-        <v>-27.88898058781413</v>
+        <v>-26.90460355039678</v>
       </c>
       <c r="F89">
-        <v>-3.916018408670071</v>
+        <v>-3.867591221935009</v>
       </c>
       <c r="G89">
-        <v>-3.923411432897099</v>
+        <v>-5.957840983145422</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.356328502652964</v>
       </c>
       <c r="E90">
-        <v>-27.16321111555282</v>
+        <v>-28.22512468492949</v>
       </c>
       <c r="F90">
-        <v>-4.369981969487061</v>
+        <v>-4.206328877022589</v>
       </c>
       <c r="G90">
-        <v>-3.506527675318836</v>
+        <v>-5.782233095014782</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.272805349019523</v>
       </c>
       <c r="E91">
-        <v>-27.56104208560066</v>
+        <v>-29.07979716981914</v>
       </c>
       <c r="F91">
-        <v>-3.571668564428525</v>
+        <v>-4.466823917446144</v>
       </c>
       <c r="G91">
-        <v>-2.9726889649292</v>
+        <v>-6.025203963778512</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.106181589598689</v>
       </c>
       <c r="E92">
-        <v>-31.00108378010543</v>
+        <v>-31.12846975394119</v>
       </c>
       <c r="F92">
-        <v>-4.190623859432913</v>
+        <v>-4.312952187273927</v>
       </c>
       <c r="G92">
-        <v>-4.495116163164919</v>
+        <v>-6.082304253239862</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.860260870247437</v>
       </c>
       <c r="E93">
-        <v>-33.67175585460303</v>
+        <v>-32.32616961643787</v>
       </c>
       <c r="F93">
-        <v>-4.39791700341167</v>
+        <v>-4.684516385799645</v>
       </c>
       <c r="G93">
-        <v>-4.02216169578802</v>
+        <v>-6.040700627447841</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.541118695397149</v>
       </c>
       <c r="E94">
-        <v>-34.26088088791989</v>
+        <v>-34.6935811078268</v>
       </c>
       <c r="F94">
-        <v>-4.095058425641545</v>
+        <v>-4.471838025335289</v>
       </c>
       <c r="G94">
-        <v>-4.731512288487657</v>
+        <v>-5.93254841522539</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.160030788449182</v>
       </c>
       <c r="E95">
-        <v>-35.84715099111872</v>
+        <v>-36.96569539219832</v>
       </c>
       <c r="F95">
-        <v>-4.308540302486617</v>
+        <v>-4.715450109722387</v>
       </c>
       <c r="G95">
-        <v>-5.002728731792449</v>
+        <v>-6.649324561569613</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.725701720929898</v>
       </c>
       <c r="E96">
-        <v>-37.85522806999902</v>
+        <v>-38.24588140874471</v>
       </c>
       <c r="F96">
-        <v>-3.9980499758345</v>
+        <v>-4.54438644247247</v>
       </c>
       <c r="G96">
-        <v>-5.223638125082476</v>
+        <v>-6.882251235167194</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.26212492967424</v>
       </c>
       <c r="E97">
-        <v>-40.75983658325886</v>
+        <v>-39.88408631610051</v>
       </c>
       <c r="F97">
-        <v>-4.26460038197252</v>
+        <v>-4.704630803074423</v>
       </c>
       <c r="G97">
-        <v>-5.243269660130355</v>
+        <v>-6.280556272859116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.777555615459419</v>
       </c>
       <c r="E98">
-        <v>-42.85539925149334</v>
+        <v>-41.94916103307835</v>
       </c>
       <c r="F98">
-        <v>-5.124970102644379</v>
+        <v>-5.1849844926098</v>
       </c>
       <c r="G98">
-        <v>-6.478030314276643</v>
+        <v>-6.971990193100218</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.302115095156153</v>
       </c>
       <c r="E99">
-        <v>-44.67333476373957</v>
+        <v>-44.29780199970549</v>
       </c>
       <c r="F99">
-        <v>-4.866954365857403</v>
+        <v>-5.196470635017018</v>
       </c>
       <c r="G99">
-        <v>-5.995217042283794</v>
+        <v>-7.735948234470134</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.834819726751279</v>
       </c>
       <c r="E100">
-        <v>-47.08044059404274</v>
+        <v>-46.27697382899483</v>
       </c>
       <c r="F100">
-        <v>-5.155365387755301</v>
+        <v>-5.462807322365115</v>
       </c>
       <c r="G100">
-        <v>-6.491388365527603</v>
+        <v>-7.649331120980642</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.425731982036122</v>
       </c>
       <c r="E101">
-        <v>-48.25767401826175</v>
+        <v>-48.15878346711924</v>
       </c>
       <c r="F101">
-        <v>-5.398921971526412</v>
+        <v>-5.559917661362704</v>
       </c>
       <c r="G101">
-        <v>-6.410766650009731</v>
+        <v>-8.143290999804218</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.034162255172675</v>
       </c>
       <c r="E102">
-        <v>-50.48899241241667</v>
+        <v>-50.98972955793332</v>
       </c>
       <c r="F102">
-        <v>-5.144146808019188</v>
+        <v>-5.623802183834004</v>
       </c>
       <c r="G102">
-        <v>-7.219297876520394</v>
+        <v>-8.52452349247007</v>
       </c>
     </row>
   </sheetData>
